--- a/Luban/Config/Datas/#WeatherConfig.xlsx
+++ b/Luban/Config/Datas/#WeatherConfig.xlsx
@@ -1,24 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\Config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{810D9458-FEEB-440F-9548-FD0735F57978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EFAE5C6-E80F-4179-BC84-B92C6F2CDC43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="-120" windowWidth="35835" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="2895" yWindow="2895" windowWidth="35565" windowHeight="9315" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -51,8 +60,9 @@
           </rPr>
           <t xml:space="preserve">
 1 - 晴
-2 - 雨
-3 - 雾</t>
+2 - 阴
+3 - 雨
+4 - 雾</t>
         </r>
       </text>
     </comment>
@@ -574,7 +584,7 @@
         <v>13</v>
       </c>
       <c r="D5" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" s="2"/>
     </row>
@@ -586,7 +596,7 @@
         <v>14</v>
       </c>
       <c r="D6" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" s="2"/>
     </row>
@@ -598,7 +608,7 @@
         <v>15</v>
       </c>
       <c r="D7" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" s="2"/>
     </row>
@@ -610,7 +620,7 @@
         <v>16</v>
       </c>
       <c r="D8" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8" s="2"/>
     </row>
@@ -622,7 +632,7 @@
         <v>17</v>
       </c>
       <c r="D9" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9" s="2"/>
     </row>
@@ -634,7 +644,7 @@
         <v>18</v>
       </c>
       <c r="D10" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" s="2"/>
     </row>
@@ -646,7 +656,7 @@
         <v>19</v>
       </c>
       <c r="D11" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" s="2"/>
     </row>
@@ -658,7 +668,7 @@
         <v>20</v>
       </c>
       <c r="D12" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" s="2"/>
     </row>
@@ -670,7 +680,7 @@
         <v>21</v>
       </c>
       <c r="D13" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E13" s="2"/>
     </row>
@@ -682,7 +692,7 @@
         <v>22</v>
       </c>
       <c r="D14" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E14" s="2"/>
     </row>
@@ -694,7 +704,7 @@
         <v>23</v>
       </c>
       <c r="D15" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E15" s="2"/>
     </row>

--- a/Luban/Config/Datas/#WeatherConfig.xlsx
+++ b/Luban/Config/Datas/#WeatherConfig.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EFAE5C6-E80F-4179-BC84-B92C6F2CDC43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="2895" yWindow="2895" windowWidth="35565" windowHeight="9315" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5565" yWindow="5790" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
